--- a/artfynd/A 12269-2022 artfynd.xlsx
+++ b/artfynd/A 12269-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 12269-2022 artfynd.xlsx
+++ b/artfynd/A 12269-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>88477756</v>
+        <v>88477763</v>
       </c>
       <c r="B2" t="n">
-        <v>77588</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83299</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>864</v>
+        <v>308</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>407342.828627101</v>
+        <v>407112</v>
       </c>
       <c r="R2" t="n">
-        <v>7012648.915445152</v>
+        <v>7012584</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -748,19 +743,9 @@
           <t>2020-10-10</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2020-10-10</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,15 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>88477757</v>
+        <v>88477755</v>
       </c>
       <c r="B3" t="n">
-        <v>81236</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79406</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -803,21 +783,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1312</v>
+        <v>864</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -827,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>407344.13065843</v>
+        <v>407363</v>
       </c>
       <c r="R3" t="n">
-        <v>7012647.073861255</v>
+        <v>7012663</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -860,19 +840,9 @@
           <t>2020-10-10</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2020-10-10</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,15 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>88477758</v>
+        <v>88477756</v>
       </c>
       <c r="B4" t="n">
-        <v>89410</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79406</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -915,21 +880,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5432</v>
+        <v>864</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -939,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>407327.0207705068</v>
+        <v>407343</v>
       </c>
       <c r="R4" t="n">
-        <v>7012648.918844986</v>
+        <v>7012649</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -972,19 +937,9 @@
           <t>2020-10-10</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2020-10-10</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1008,6 +963,709 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>88477760</v>
+      </c>
+      <c r="B5" t="n">
+        <v>91923</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>1204</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Gränsticka</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Phellopilus nigrolimitatus</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Vägskälsskogen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>407258</v>
+      </c>
+      <c r="R5" t="n">
+        <v>7012613</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Undersåker</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2020-10-10</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2020-10-10</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Johan Råghall</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Johan Råghall</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>88477757</v>
+      </c>
+      <c r="B6" t="n">
+        <v>83173</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>1312</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Gammelgransskål</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Pseudographis pinicola</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Nyl.) Rehm</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Vägskälsskogen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>407344</v>
+      </c>
+      <c r="R6" t="n">
+        <v>7012647</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Undersåker</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2020-10-10</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2020-10-10</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Johan Råghall</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Johan Råghall</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>88477772</v>
+      </c>
+      <c r="B7" t="n">
+        <v>83173</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>1312</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Gammelgransskål</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Pseudographis pinicola</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Nyl.) Rehm</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Vägskälsskogen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>407478</v>
+      </c>
+      <c r="R7" t="n">
+        <v>7012615</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Undersåker</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2020-10-10</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2020-10-10</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Johan Råghall</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Johan Råghall</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>88477764</v>
+      </c>
+      <c r="B8" t="n">
+        <v>83312</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>1467</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Rödbrun blekspik</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Sclerophora coniophaea</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Vägskälsskogen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>407115</v>
+      </c>
+      <c r="R8" t="n">
+        <v>7012580</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Undersåker</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2020-10-10</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2020-10-10</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Johan Råghall</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Johan Råghall</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>87165198</v>
+      </c>
+      <c r="B9" t="n">
+        <v>93215</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>4368</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Dofttaggsvamp</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Hydnellum suaveolens</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Scop.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Sätteråvallen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>406959</v>
+      </c>
+      <c r="R9" t="n">
+        <v>7012646</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Undersåker</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2020-07-29</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>20:19</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2020-07-29</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>20:19</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Mellan vallen och ån.</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Johan Råghall</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Johan Råghall, Ingela Källén</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>88477773</v>
+      </c>
+      <c r="B10" t="n">
+        <v>83307</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>6440</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Vitgrynig nållav</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Chaenotheca subroscida</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Vägskälsskogen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>407483</v>
+      </c>
+      <c r="R10" t="n">
+        <v>7012608</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Undersåker</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2020-10-10</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2020-10-10</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Johan Råghall</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Johan Råghall</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>88477771</v>
+      </c>
+      <c r="B11" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Vägskälsskogen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>407382</v>
+      </c>
+      <c r="R11" t="n">
+        <v>7012569</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Undersåker</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2020-10-10</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2020-10-10</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Johan Råghall</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Johan Råghall</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 12269-2022 artfynd.xlsx
+++ b/artfynd/A 12269-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY11"/>
+  <dimension ref="A1:AZ11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/88477763</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/88477755</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,6 +978,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/88477756</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1060,6 +1080,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/88477760</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1157,6 +1182,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/88477757</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1254,6 +1284,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/88477772</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1351,6 +1386,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/88477764</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1464,6 +1504,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/87165198</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1561,6 +1606,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/88477773</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1666,8 +1716,25 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/88477771</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>